--- a/Libro6.xlsx
+++ b/Libro6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanignaciomartinez/Desktop/UnidadNueva/UnidadNueva/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106B83E6-5B05-E649-8000-FC730E17BEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E676D171-1E9C-394F-92DE-E847A6BA9486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2380" windowWidth="27640" windowHeight="16680" xr2:uid="{167BE71C-E033-8A42-A00A-646ACDCB5A62}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>cuervo anonimo</t>
   </si>
@@ -59,76 +59,36 @@
     <t>UNIDAD NUEVA</t>
   </si>
   <si>
-    <t>Tiktok España</t>
-  </si>
-  <si>
-    <t>sacar sustitutivo</t>
-  </si>
-  <si>
-    <t>Juan Barber armada ; Huertas 26, 2B ; 28220 ; Majadahonda ; Madrid ; 609982119</t>
-  </si>
-  <si>
-    <t>MANOMANO FR</t>
-  </si>
-  <si>
     <t>NO TIENE</t>
   </si>
   <si>
-    <t>M260388520343</t>
-  </si>
-  <si>
-    <t>Marine Buisson ; 21 rue Louise de savoie ; 01160 ; Pont-d'Ain ; Francia ; 
-+33626811715</t>
-  </si>
-  <si>
-    <t>M260388526093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AnneValerie Dragaut ; 6 rue du château ; 77300 ; Fontainebleau ; Francia ;
-+33780996553
-</t>
-  </si>
-  <si>
-    <t>SHOWROOM</t>
-  </si>
-  <si>
-    <t>A-4452862-1-A</t>
-  </si>
-  <si>
-    <t>A01_EU01_100011</t>
-  </si>
-  <si>
-    <t>Liliana Rebel ; Calle Eiras nº5 ; 6440-261 ; Vermiosa ; Portugal ; 965012830</t>
-  </si>
-  <si>
-    <t>AMAZON TURACO ES</t>
-  </si>
-  <si>
-    <t>408-1599273-9581128</t>
-  </si>
-  <si>
-    <t>S01522</t>
-  </si>
-  <si>
-    <t>Laura Patricia Novoa Rial ;
-Travesía de Bellomonte, 1, 3°A;
-Chapinería; Madrid; 28694; 
-España; 605329487</t>
-  </si>
-  <si>
-    <t>AMAZON Jabiru ES</t>
-  </si>
-  <si>
-    <t>407-7424620-9791510</t>
-  </si>
-  <si>
-    <t>A90_EU01_100500</t>
-  </si>
-  <si>
-    <t>Angie ; Calle agustín Fernández García 19 primera derecha ; 16235 ; Iniesta ; Cuenca ;</t>
-  </si>
-  <si>
     <t>notas</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>22-14327-93126</t>
+  </si>
+  <si>
+    <t>Carlos Lechosa Urquijo ; +34 637 56 34 79 ; Calle De Alfonso Viii 7 Bajo D ; 28806 ; Alcalá De Henares ; España</t>
+  </si>
+  <si>
+    <t>Cdiscount</t>
+  </si>
+  <si>
+    <t>2603030302OS8YB</t>
+  </si>
+  <si>
+    <t>A01_EU01_107958</t>
+  </si>
+  <si>
+    <t>Mme SETTOUTI Kenza ;
+0764487166 ;
+158 Chemin De Blory ;
+57950 ;
+Montigny Les Metz ;
+FR</t>
   </si>
 </sst>
 </file>
@@ -518,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17C343B-17CF-A34F-9EB1-EAB4A7559DEE}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -544,137 +504,49 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2">
-        <v>5.7686860639735603E+17</v>
-      </c>
-      <c r="E2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1003</v>
+      </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="127" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="155" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1712</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="155" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2">
-        <v>3815</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1431520</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="155" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1436914</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1217503</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
